--- a/lab_07_basic.xlsx
+++ b/lab_07_basic.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shreena\OneDrive\Desktop\office automation tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F431A2-E8B1-402C-B2EE-57E1A11F4FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FA55F3-B8AD-4A93-AB19-E2BF3C83E078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{CE618516-17FC-4E07-8155-E73A2CA0EE16}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{CE618516-17FC-4E07-8155-E73A2CA0EE16}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$3:$G$18</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
   <si>
     <t>Student Name</t>
   </si>
@@ -111,13 +112,40 @@
   </si>
   <si>
     <t>Student Marksheet</t>
+  </si>
+  <si>
+    <t>Final Examiantion Result</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Percentage</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>Minimum</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upper </t>
+  </si>
+  <si>
+    <t>Lower</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,8 +182,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="2"/>
+      <name val="Cascadia Code ExtraLight"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -177,6 +218,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -205,11 +252,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -222,15 +276,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -573,392 +628,392 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="6">
+      <c r="A4" s="2">
         <v>101</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="2">
         <v>55</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="2">
         <v>62</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="2">
         <v>71</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="2">
         <v>68</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="2">
         <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
+      <c r="A5" s="2">
         <v>107</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="2">
         <v>75</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="2">
         <v>82</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="2">
         <v>78</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="2">
         <v>74</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="2">
         <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="6">
+      <c r="A6" s="2">
         <v>109</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="2">
         <v>81</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="2">
         <v>79</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="2">
         <v>82</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="2">
         <v>80</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="2">
         <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
+      <c r="A7" s="2">
         <v>104</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="2">
         <v>78</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="2">
         <v>85</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="2">
         <v>92</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="2">
         <v>88</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="2">
         <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="6">
+      <c r="A8" s="2">
         <v>110</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="2">
         <v>90</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="2">
         <v>88</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="2">
         <v>95</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="2">
         <v>91</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="2">
         <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="6">
+      <c r="A9" s="2">
         <v>113</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="2">
         <v>89</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="2">
         <v>87</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="2">
         <v>91</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="2">
         <v>85</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="2">
         <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="6">
+      <c r="A10" s="2">
         <v>115</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="2">
         <v>94</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="2">
         <v>91</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="2">
         <v>96</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="2">
         <v>93</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="2">
         <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="6">
+      <c r="A11" s="2">
         <v>103</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="2">
         <v>65</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="2">
         <v>72</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="2">
         <v>80</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="2">
         <v>75</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="2">
         <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="6">
+      <c r="A12" s="2">
         <v>105</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="2">
         <v>70</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="2">
         <v>65</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="2">
         <v>72</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="2">
         <v>68</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="2">
         <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="6">
+      <c r="A13" s="2">
         <v>106</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="2">
         <v>72</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="2">
         <v>84</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="2">
         <v>79</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="2">
         <v>82</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="2">
         <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="6">
+      <c r="A14" s="2">
         <v>111</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="2">
         <v>88</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="2">
         <v>90</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="2">
         <v>85</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="2">
         <v>92</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="2">
         <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="6">
+      <c r="A15" s="2">
         <v>114</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="2">
         <v>82</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="2">
         <v>76</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="2">
         <v>89</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="2">
         <v>84</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="2">
         <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="6">
+      <c r="A16" s="2">
         <v>108</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="2">
         <v>84</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="2">
         <v>80</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="2">
         <v>85</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="2">
         <v>78</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="2">
         <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="6">
+      <c r="A17" s="2">
         <v>112</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="2">
         <v>92</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="2">
         <v>95</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="2">
         <v>88</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="2">
         <v>91</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="2">
         <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="6">
+      <c r="A18" s="2">
         <v>102</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="2">
         <v>60</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="2">
         <v>68</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="2">
         <v>65</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="2">
         <v>72</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="2">
         <v>64</v>
       </c>
     </row>
@@ -984,4 +1039,944 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44AE613E-7363-4793-9BC0-ED43736BC785}">
+  <dimension ref="A1:O18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.08984375" customWidth="1"/>
+    <col min="2" max="2" width="17.90625" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" customWidth="1"/>
+    <col min="4" max="4" width="11.26953125" customWidth="1"/>
+    <col min="5" max="5" width="10.90625" customWidth="1"/>
+    <col min="6" max="6" width="11.6328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="8" width="12.36328125" customWidth="1"/>
+    <col min="9" max="13" width="13.36328125" customWidth="1"/>
+    <col min="14" max="14" width="15.7265625" customWidth="1"/>
+    <col min="15" max="15" width="13.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+    </row>
+    <row r="2" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>101</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>55</v>
+      </c>
+      <c r="D4" s="2">
+        <v>62</v>
+      </c>
+      <c r="E4" s="2">
+        <v>71</v>
+      </c>
+      <c r="F4" s="2">
+        <v>68</v>
+      </c>
+      <c r="G4" s="2">
+        <v>60</v>
+      </c>
+      <c r="H4" s="2">
+        <f>SUM(C4:G4)</f>
+        <v>316</v>
+      </c>
+      <c r="I4" s="2">
+        <f>AVERAGE(C4:G4)</f>
+        <v>63.2</v>
+      </c>
+      <c r="J4" s="8">
+        <f>AVERAGE(C4:G4)/100</f>
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="K4" s="2">
+        <f>MAX(C4:G4)</f>
+        <v>71</v>
+      </c>
+      <c r="L4" s="2">
+        <f>MIN(C4:G4)</f>
+        <v>55</v>
+      </c>
+      <c r="M4" s="2">
+        <f>COUNT(C4:G4)</f>
+        <v>5</v>
+      </c>
+      <c r="N4" s="2" t="str">
+        <f>UPPER(B4)</f>
+        <v>AARAV SHARMA</v>
+      </c>
+      <c r="O4" s="2" t="str">
+        <f>LOWER(B4)</f>
+        <v>aarav sharma</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>107</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2">
+        <v>75</v>
+      </c>
+      <c r="D5" s="2">
+        <v>82</v>
+      </c>
+      <c r="E5" s="2">
+        <v>78</v>
+      </c>
+      <c r="F5" s="2">
+        <v>74</v>
+      </c>
+      <c r="G5" s="2">
+        <v>81</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" ref="H5:H18" si="0">SUM(C5:G5)</f>
+        <v>390</v>
+      </c>
+      <c r="I5" s="2">
+        <f t="shared" ref="I5:I18" si="1">AVERAGE(C5:G5)</f>
+        <v>78</v>
+      </c>
+      <c r="J5" s="8">
+        <f t="shared" ref="J5:J18" si="2">AVERAGE(C5:G5)/100</f>
+        <v>0.78</v>
+      </c>
+      <c r="K5" s="2">
+        <f t="shared" ref="K5:K18" si="3">MAX(C5:G5)</f>
+        <v>82</v>
+      </c>
+      <c r="L5" s="2">
+        <f t="shared" ref="L5:L18" si="4">MIN(C5:G5)</f>
+        <v>74</v>
+      </c>
+      <c r="M5" s="2">
+        <f t="shared" ref="M5:M18" si="5">COUNT(C5:G5)</f>
+        <v>5</v>
+      </c>
+      <c r="N5" s="2" t="str">
+        <f t="shared" ref="N5:N18" si="6">UPPER(B5)</f>
+        <v>AARUSH REDDY</v>
+      </c>
+      <c r="O5" s="2" t="str">
+        <f t="shared" ref="O5:O18" si="7">LOWER(B5)</f>
+        <v>aarush reddy</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>109</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2">
+        <v>81</v>
+      </c>
+      <c r="D6" s="2">
+        <v>79</v>
+      </c>
+      <c r="E6" s="2">
+        <v>82</v>
+      </c>
+      <c r="F6" s="2">
+        <v>80</v>
+      </c>
+      <c r="G6" s="2">
+        <v>85</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="0"/>
+        <v>407</v>
+      </c>
+      <c r="I6" s="2">
+        <f t="shared" si="1"/>
+        <v>81.400000000000006</v>
+      </c>
+      <c r="J6" s="8">
+        <f t="shared" si="2"/>
+        <v>0.81400000000000006</v>
+      </c>
+      <c r="K6" s="2">
+        <f t="shared" si="3"/>
+        <v>85</v>
+      </c>
+      <c r="L6" s="2">
+        <f t="shared" si="4"/>
+        <v>79</v>
+      </c>
+      <c r="M6" s="2">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="N6" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>ADITYA MEHTA</v>
+      </c>
+      <c r="O6" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>aditya mehta</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>104</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2">
+        <v>78</v>
+      </c>
+      <c r="D7" s="2">
+        <v>85</v>
+      </c>
+      <c r="E7" s="2">
+        <v>92</v>
+      </c>
+      <c r="F7" s="2">
+        <v>88</v>
+      </c>
+      <c r="G7" s="2">
+        <v>74</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="0"/>
+        <v>417</v>
+      </c>
+      <c r="I7" s="2">
+        <f t="shared" si="1"/>
+        <v>83.4</v>
+      </c>
+      <c r="J7" s="8">
+        <f t="shared" si="2"/>
+        <v>0.83400000000000007</v>
+      </c>
+      <c r="K7" s="2">
+        <f t="shared" si="3"/>
+        <v>92</v>
+      </c>
+      <c r="L7" s="2">
+        <f t="shared" si="4"/>
+        <v>74</v>
+      </c>
+      <c r="M7" s="2">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="N7" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>ANANYA SHARMA</v>
+      </c>
+      <c r="O7" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>ananya sharma</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>110</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2">
+        <v>90</v>
+      </c>
+      <c r="D8" s="2">
+        <v>88</v>
+      </c>
+      <c r="E8" s="2">
+        <v>95</v>
+      </c>
+      <c r="F8" s="2">
+        <v>91</v>
+      </c>
+      <c r="G8" s="2">
+        <v>85</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="0"/>
+        <v>449</v>
+      </c>
+      <c r="I8" s="2">
+        <f t="shared" si="1"/>
+        <v>89.8</v>
+      </c>
+      <c r="J8" s="8">
+        <f t="shared" si="2"/>
+        <v>0.89800000000000002</v>
+      </c>
+      <c r="K8" s="2">
+        <f t="shared" si="3"/>
+        <v>95</v>
+      </c>
+      <c r="L8" s="2">
+        <f t="shared" si="4"/>
+        <v>85</v>
+      </c>
+      <c r="M8" s="2">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="N8" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>ANIKA JOSHI</v>
+      </c>
+      <c r="O8" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>anika joshi</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>113</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2">
+        <v>89</v>
+      </c>
+      <c r="D9" s="2">
+        <v>87</v>
+      </c>
+      <c r="E9" s="2">
+        <v>91</v>
+      </c>
+      <c r="F9" s="2">
+        <v>85</v>
+      </c>
+      <c r="G9" s="2">
+        <v>90</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="0"/>
+        <v>442</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" si="1"/>
+        <v>88.4</v>
+      </c>
+      <c r="J9" s="8">
+        <f t="shared" si="2"/>
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="K9" s="2">
+        <f t="shared" si="3"/>
+        <v>91</v>
+      </c>
+      <c r="L9" s="2">
+        <f t="shared" si="4"/>
+        <v>85</v>
+      </c>
+      <c r="M9" s="2">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="N9" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>ARJUN IYER</v>
+      </c>
+      <c r="O9" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>arjun iyer</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>115</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2">
+        <v>94</v>
+      </c>
+      <c r="D10" s="2">
+        <v>91</v>
+      </c>
+      <c r="E10" s="2">
+        <v>96</v>
+      </c>
+      <c r="F10" s="2">
+        <v>93</v>
+      </c>
+      <c r="G10" s="2">
+        <v>92</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="0"/>
+        <v>466</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="1"/>
+        <v>93.2</v>
+      </c>
+      <c r="J10" s="8">
+        <f t="shared" si="2"/>
+        <v>0.93200000000000005</v>
+      </c>
+      <c r="K10" s="2">
+        <f t="shared" si="3"/>
+        <v>96</v>
+      </c>
+      <c r="L10" s="2">
+        <f t="shared" si="4"/>
+        <v>91</v>
+      </c>
+      <c r="M10" s="2">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="N10" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>DEVENDRA RAO</v>
+      </c>
+      <c r="O10" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>devendra rao</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>103</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2">
+        <v>65</v>
+      </c>
+      <c r="D11" s="2">
+        <v>72</v>
+      </c>
+      <c r="E11" s="2">
+        <v>80</v>
+      </c>
+      <c r="F11" s="2">
+        <v>75</v>
+      </c>
+      <c r="G11" s="2">
+        <v>70</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="0"/>
+        <v>362</v>
+      </c>
+      <c r="I11" s="2">
+        <f t="shared" si="1"/>
+        <v>72.400000000000006</v>
+      </c>
+      <c r="J11" s="8">
+        <f t="shared" si="2"/>
+        <v>0.72400000000000009</v>
+      </c>
+      <c r="K11" s="2">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="L11" s="2">
+        <f t="shared" si="4"/>
+        <v>65</v>
+      </c>
+      <c r="M11" s="2">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="N11" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>DIYA SINGH</v>
+      </c>
+      <c r="O11" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>diya singh</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>105</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2">
+        <v>70</v>
+      </c>
+      <c r="D12" s="2">
+        <v>65</v>
+      </c>
+      <c r="E12" s="2">
+        <v>72</v>
+      </c>
+      <c r="F12" s="2">
+        <v>68</v>
+      </c>
+      <c r="G12" s="2">
+        <v>75</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="J12" s="8">
+        <f t="shared" si="2"/>
+        <v>0.7</v>
+      </c>
+      <c r="K12" s="2">
+        <f t="shared" si="3"/>
+        <v>75</v>
+      </c>
+      <c r="L12" s="2">
+        <f t="shared" si="4"/>
+        <v>65</v>
+      </c>
+      <c r="M12" s="2">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="N12" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>ISHAAN VERMA</v>
+      </c>
+      <c r="O12" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>ishaan verma</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>106</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2">
+        <v>72</v>
+      </c>
+      <c r="D13" s="2">
+        <v>84</v>
+      </c>
+      <c r="E13" s="2">
+        <v>79</v>
+      </c>
+      <c r="F13" s="2">
+        <v>82</v>
+      </c>
+      <c r="G13" s="2">
+        <v>77</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="0"/>
+        <v>394</v>
+      </c>
+      <c r="I13" s="2">
+        <f t="shared" si="1"/>
+        <v>78.8</v>
+      </c>
+      <c r="J13" s="8">
+        <f t="shared" si="2"/>
+        <v>0.78799999999999992</v>
+      </c>
+      <c r="K13" s="2">
+        <f t="shared" si="3"/>
+        <v>84</v>
+      </c>
+      <c r="L13" s="2">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="M13" s="2">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="N13" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>KAVYA PATEL</v>
+      </c>
+      <c r="O13" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>kavya patel</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>111</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2">
+        <v>88</v>
+      </c>
+      <c r="D14" s="2">
+        <v>90</v>
+      </c>
+      <c r="E14" s="2">
+        <v>85</v>
+      </c>
+      <c r="F14" s="2">
+        <v>92</v>
+      </c>
+      <c r="G14" s="2">
+        <v>87</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="0"/>
+        <v>442</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" si="1"/>
+        <v>88.4</v>
+      </c>
+      <c r="J14" s="8">
+        <f t="shared" si="2"/>
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="K14" s="2">
+        <f t="shared" si="3"/>
+        <v>92</v>
+      </c>
+      <c r="L14" s="2">
+        <f t="shared" si="4"/>
+        <v>85</v>
+      </c>
+      <c r="M14" s="2">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="N14" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>KRISHNA KUMAR</v>
+      </c>
+      <c r="O14" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>krishna kumar</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>114</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="2">
+        <v>82</v>
+      </c>
+      <c r="D15" s="2">
+        <v>76</v>
+      </c>
+      <c r="E15" s="2">
+        <v>89</v>
+      </c>
+      <c r="F15" s="2">
+        <v>84</v>
+      </c>
+      <c r="G15" s="2">
+        <v>91</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="0"/>
+        <v>422</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" si="1"/>
+        <v>84.4</v>
+      </c>
+      <c r="J15" s="8">
+        <f t="shared" si="2"/>
+        <v>0.84400000000000008</v>
+      </c>
+      <c r="K15" s="2">
+        <f t="shared" si="3"/>
+        <v>91</v>
+      </c>
+      <c r="L15" s="2">
+        <f t="shared" si="4"/>
+        <v>76</v>
+      </c>
+      <c r="M15" s="2">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="N15" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>MEERA NAIR</v>
+      </c>
+      <c r="O15" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>meera nair</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>108</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="2">
+        <v>84</v>
+      </c>
+      <c r="D16" s="2">
+        <v>80</v>
+      </c>
+      <c r="E16" s="2">
+        <v>85</v>
+      </c>
+      <c r="F16" s="2">
+        <v>78</v>
+      </c>
+      <c r="G16" s="2">
+        <v>82</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="0"/>
+        <v>409</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="1"/>
+        <v>81.8</v>
+      </c>
+      <c r="J16" s="8">
+        <f t="shared" si="2"/>
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="K16" s="2">
+        <f t="shared" si="3"/>
+        <v>85</v>
+      </c>
+      <c r="L16" s="2">
+        <f t="shared" si="4"/>
+        <v>78</v>
+      </c>
+      <c r="M16" s="2">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="N16" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>SHANAYA SHAH</v>
+      </c>
+      <c r="O16" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>shanaya shah</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>112</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="2">
+        <v>92</v>
+      </c>
+      <c r="D17" s="2">
+        <v>95</v>
+      </c>
+      <c r="E17" s="2">
+        <v>88</v>
+      </c>
+      <c r="F17" s="2">
+        <v>91</v>
+      </c>
+      <c r="G17" s="2">
+        <v>89</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="0"/>
+        <v>455</v>
+      </c>
+      <c r="I17" s="2">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="J17" s="8">
+        <f t="shared" si="2"/>
+        <v>0.91</v>
+      </c>
+      <c r="K17" s="2">
+        <f t="shared" si="3"/>
+        <v>95</v>
+      </c>
+      <c r="L17" s="2">
+        <f t="shared" si="4"/>
+        <v>88</v>
+      </c>
+      <c r="M17" s="2">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="N17" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>SIYA DESAI</v>
+      </c>
+      <c r="O17" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>siya desai</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>102</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2">
+        <v>60</v>
+      </c>
+      <c r="D18" s="2">
+        <v>68</v>
+      </c>
+      <c r="E18" s="2">
+        <v>65</v>
+      </c>
+      <c r="F18" s="2">
+        <v>72</v>
+      </c>
+      <c r="G18" s="2">
+        <v>64</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="0"/>
+        <v>329</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="1"/>
+        <v>65.8</v>
+      </c>
+      <c r="J18" s="8">
+        <f t="shared" si="2"/>
+        <v>0.65799999999999992</v>
+      </c>
+      <c r="K18" s="2">
+        <f t="shared" si="3"/>
+        <v>72</v>
+      </c>
+      <c r="L18" s="2">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="M18" s="2">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="N18" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>VIVAAN GUPTA</v>
+      </c>
+      <c r="O18" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>vivaan gupta</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter marks between 33 and 100" sqref="C4:G18" xr:uid="{8308021D-1BF5-46B8-841E-CD615DE6D00F}">
+      <formula1>33</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>